--- a/bus-raspberry/Routes.xlsx
+++ b/bus-raspberry/Routes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugk\Documents\iot\project\code\busai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugk\Documents\iot\project\code\bus-raspberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E314B88F-72B5-45AE-8F50-B1C134F6BA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05525BA2-51A2-40A3-A74B-F78BAEEA0287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E451EE4A-2127-43C9-9A50-5536E739BF9B}"/>
+    <workbookView xWindow="696" yWindow="2472" windowWidth="21468" windowHeight="9084" xr2:uid="{E451EE4A-2127-43C9-9A50-5536E739BF9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,107 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="216">
-  <si>
-    <t>Ερμού</t>
-  </si>
-  <si>
-    <t>Αγίου Νικολάου</t>
-  </si>
-  <si>
-    <t>Ζαΐμη</t>
-  </si>
-  <si>
-    <t>Παλιό Αρσάκειο</t>
-  </si>
-  <si>
-    <t>Πλατεία Πυροσβεστείου</t>
-  </si>
-  <si>
-    <t>Φαβιέρου</t>
-  </si>
-  <si>
-    <t>Μαράτου</t>
-  </si>
-  <si>
-    <t>Κουρτέση</t>
-  </si>
-  <si>
-    <t>Φίλιππα</t>
-  </si>
-  <si>
-    <t>Α' Νεκροταφείο</t>
-  </si>
-  <si>
-    <t>Ανθούπολη</t>
-  </si>
-  <si>
-    <t>ΟΓΑ</t>
-  </si>
-  <si>
-    <t>Αρέθα (προς Πανεπιστήμιο)</t>
-  </si>
-  <si>
-    <t>Αρέθα</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="186">
   <si>
     <t>Intracom</t>
   </si>
   <si>
-    <t>Κοτρώνι</t>
-  </si>
-  <si>
-    <t>Μηχανική Καλλιέργεια 1</t>
-  </si>
-  <si>
-    <t>Μηχανική Καλλιέργεια 2</t>
-  </si>
-  <si>
-    <t>Κορυδαλλέως</t>
-  </si>
-  <si>
-    <t>Ψησταριά</t>
-  </si>
-  <si>
-    <t>Βησσαρίωνος</t>
-  </si>
-  <si>
-    <t>Προάστιο</t>
-  </si>
-  <si>
-    <t>Μανδρέκα</t>
-  </si>
-  <si>
-    <t>Γήπεδο Τόφαλος</t>
-  </si>
-  <si>
-    <t>Ποταμός Χάραδρος</t>
-  </si>
-  <si>
-    <t>Πρυτανεία Πανεπιστημίου Πατρών</t>
-  </si>
-  <si>
-    <t>Πολυτεχνείο</t>
-  </si>
-  <si>
-    <t>Συνεδριακό Κέντρο</t>
-  </si>
-  <si>
-    <t>Φυσικό</t>
-  </si>
-  <si>
-    <t>Γεωλογικό</t>
-  </si>
-  <si>
-    <t>Ιατρική</t>
-  </si>
-  <si>
-    <t>Νοσοκομείο</t>
-  </si>
-  <si>
-    <t>Locations</t>
-  </si>
-  <si>
     <t>38.24674692664068, 21.73598679633868</t>
   </si>
   <si>
@@ -590,9 +494,6 @@
     <t>38.24675716463252, 21.73601647936283</t>
   </si>
   <si>
-    <t>Stations</t>
-  </si>
-  <si>
     <t>Ermou</t>
   </si>
   <si>
@@ -684,6 +585,15 @@
   </si>
   <si>
     <t>Hospital</t>
+  </si>
+  <si>
+    <t>Station's Location</t>
+  </si>
+  <si>
+    <t>Station</t>
+  </si>
+  <si>
+    <t>Location</t>
   </si>
 </sst>
 </file>
@@ -1076,1276 +986,1212 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
         <v>184</v>
       </c>
-      <c r="G1" t="s">
-        <v>184</v>
+      <c r="D1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G29" s="1"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G32" s="1"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G35" s="1"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="G40" s="1"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>13</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="G46" s="1"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G49" s="1"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="D60" t="s">
-        <v>90</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G60" s="1"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D64" t="s">
-        <v>95</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="D66" t="s">
-        <v>96</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="D69" t="s">
-        <v>97</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="D74" t="s">
-        <v>98</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="D79" t="s">
-        <v>99</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="D83" t="s">
-        <v>100</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="D87" t="s">
-        <v>101</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G87" s="1"/>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="D104" t="s">
-        <v>102</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G104" s="1"/>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="D106" t="s">
-        <v>103</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="G106" s="1"/>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="D108" t="s">
-        <v>104</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G108" s="1"/>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="D113" t="s">
-        <v>105</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G113" s="1"/>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="D117" t="s">
-        <v>106</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G117" s="1"/>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="D119" t="s">
-        <v>107</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G119" s="1"/>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G123" s="1"/>
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C124" s="1"/>

--- a/bus-raspberry/Routes.xlsx
+++ b/bus-raspberry/Routes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugk\Documents\iot\project\code\bus-raspberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugk\Documents\iot\project\code\Pan\BR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05525BA2-51A2-40A3-A74B-F78BAEEA0287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0485752-0ADD-46D1-952D-0038976B74B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="696" yWindow="2472" windowWidth="21468" windowHeight="9084" xr2:uid="{E451EE4A-2127-43C9-9A50-5536E739BF9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E451EE4A-2127-43C9-9A50-5536E739BF9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="198">
   <si>
     <t>Intracom</t>
   </si>
@@ -506,9 +506,6 @@
     <t>Aretha</t>
   </si>
   <si>
-    <t>Aretha (to University)</t>
-  </si>
-  <si>
     <t>Kotroni</t>
   </si>
   <si>
@@ -536,9 +533,6 @@
     <t>Tofalos Stadium</t>
   </si>
   <si>
-    <t>University of Patras Chancellor's Office</t>
-  </si>
-  <si>
     <t>Old Arsakeio</t>
   </si>
   <si>
@@ -594,6 +588,48 @@
   </si>
   <si>
     <t>Location</t>
+  </si>
+  <si>
+    <t>Aretha to University</t>
+  </si>
+  <si>
+    <t>University of Patras Chancellors Office</t>
+  </si>
+  <si>
+    <t>13:38:00 PM</t>
+  </si>
+  <si>
+    <t>13:39:00 PM</t>
+  </si>
+  <si>
+    <t>13:40:00 AM</t>
+  </si>
+  <si>
+    <t>13:41:00 AM</t>
+  </si>
+  <si>
+    <t>13:42:00 AM</t>
+  </si>
+  <si>
+    <t>13:43:00 PM</t>
+  </si>
+  <si>
+    <t>13:43:20 AM</t>
+  </si>
+  <si>
+    <t>13:43:30 AM</t>
+  </si>
+  <si>
+    <t>13:44:00 AM</t>
+  </si>
+  <si>
+    <t>5,6</t>
+  </si>
+  <si>
+    <t>7,8</t>
+  </si>
+  <si>
+    <t>10,11</t>
   </si>
 </sst>
 </file>
@@ -634,12 +670,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,28 +1016,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4684BDE6-A2E5-43EE-9007-9CE737092BA5}">
-  <dimension ref="B1:G124"/>
+  <dimension ref="B1:K124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>151</v>
       </c>
@@ -1005,10 +1056,29 @@
       <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E2" s="2">
+        <v>0.23263888888888887</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.31597222222222221</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.44097222222222227</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.81597222222222221</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.94097222222222221</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1018,8 +1088,29 @@
       <c r="D3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -1029,8 +1120,29 @@
       <c r="D4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>150</v>
       </c>
@@ -1040,9 +1152,29 @@
       <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E5" s="2">
+        <v>0.23333333333333331</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.31666666666666665</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.23333333333333331</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.23333333333333331</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.23333333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1052,8 +1184,29 @@
       <c r="D6" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -1063,8 +1216,29 @@
       <c r="D7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>149</v>
       </c>
@@ -1074,9 +1248,29 @@
       <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E8" s="4">
+        <v>0.23402777777777781</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.31736111111111115</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.44236111111111115</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.23402777777777781</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.23402777777777781</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.23402777777777781</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1086,8 +1280,29 @@
       <c r="D9" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>9</v>
       </c>
@@ -1097,20 +1312,61 @@
       <c r="D10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>148</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E11" s="2">
+        <v>0.23472222222222219</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.31805555555555554</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.23472222222222219</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.23472222222222219</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.23472222222222219</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1120,8 +1376,29 @@
       <c r="D12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1131,8 +1408,29 @@
       <c r="D13" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1142,20 +1440,61 @@
       <c r="D14" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>147</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E15" s="2">
+        <v>0.23541666666666669</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.31875000000000003</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.44375000000000003</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.23541666666666669</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.23541666666666669</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.23541666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1165,8 +1504,29 @@
       <c r="D16" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>16</v>
       </c>
@@ -1176,20 +1536,61 @@
       <c r="D17" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>146</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E18" s="2">
+        <v>0.23611111111111113</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.31944444444444448</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.23611111111111113</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.23611111111111113</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.23611111111111113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1199,8 +1600,29 @@
       <c r="D19" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>19</v>
       </c>
@@ -1210,20 +1632,61 @@
       <c r="D20" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>145</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E21" s="5">
+        <v>0.23680555555555557</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0.32013888888888892</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.44513888888888892</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.23680555555555557</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0.23680555555555557</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0.23680555555555557</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1233,8 +1696,29 @@
       <c r="D22" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s">
+        <v>77</v>
+      </c>
+      <c r="K22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>22</v>
       </c>
@@ -1244,8 +1728,29 @@
       <c r="D23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>23</v>
       </c>
@@ -1255,20 +1760,61 @@
       <c r="D24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s">
+        <v>77</v>
+      </c>
+      <c r="K24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>144</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E25" s="2">
+        <v>0.23750000000000002</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.32083333333333336</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0.4458333333333333</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0.23750000000000002</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0.23750000000000002</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.23750000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,8 +1824,29 @@
       <c r="D26" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s">
+        <v>77</v>
+      </c>
+      <c r="J26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>26</v>
       </c>
@@ -1289,8 +1856,29 @@
       <c r="D27" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s">
+        <v>77</v>
+      </c>
+      <c r="J27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1300,20 +1888,61 @@
       <c r="D28" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>143</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E29" s="2">
+        <v>0.23819444444444446</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.3215277777777778</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.4465277777777778</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.23819444444444446</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0.23819444444444446</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0.23819444444444446</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>29</v>
       </c>
@@ -1323,8 +1952,29 @@
       <c r="D30" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1334,20 +1984,61 @@
       <c r="D31" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s">
+        <v>77</v>
+      </c>
+      <c r="K31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>142</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E32" s="2">
+        <v>0.23842592592592593</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.32175925925925924</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.44675925925925924</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0.23842592592592593</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0.23842592592592593</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0.23842592592592593</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>32</v>
       </c>
@@ -1357,8 +2048,29 @@
       <c r="D33" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>33</v>
       </c>
@@ -1368,20 +2080,61 @@
       <c r="D34" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s">
+        <v>77</v>
+      </c>
+      <c r="K34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>141</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E35" s="2">
+        <v>0.23854166666666665</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.32187499999999997</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.44687499999999997</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.23854166666666665</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0.23854166666666665</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0.23854166666666665</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>35</v>
       </c>
@@ -1391,8 +2144,29 @@
       <c r="D36" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>36</v>
       </c>
@@ -1402,8 +2176,29 @@
       <c r="D37" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" t="s">
+        <v>77</v>
+      </c>
+      <c r="H37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" t="s">
+        <v>77</v>
+      </c>
+      <c r="J37" t="s">
+        <v>77</v>
+      </c>
+      <c r="K37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
@@ -1413,8 +2208,29 @@
       <c r="D38" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>38</v>
       </c>
@@ -1424,20 +2240,61 @@
       <c r="D39" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" t="s">
+        <v>77</v>
+      </c>
+      <c r="J39" t="s">
+        <v>77</v>
+      </c>
+      <c r="K39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>140</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
       </c>
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E40" s="2">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.32222222222222224</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.44722222222222219</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0.2388888888888889</v>
+      </c>
+      <c r="K40" s="2">
+        <v>0.2388888888888889</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
@@ -1447,8 +2304,29 @@
       <c r="D41" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" t="s">
+        <v>77</v>
+      </c>
+      <c r="H41" t="s">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s">
+        <v>77</v>
+      </c>
+      <c r="K41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>41</v>
       </c>
@@ -1458,20 +2336,61 @@
       <c r="D42" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" t="s">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s">
+        <v>77</v>
+      </c>
+      <c r="J42" t="s">
+        <v>77</v>
+      </c>
+      <c r="K42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>139</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E43" s="2">
+        <v>0.23923611111111112</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0.32256944444444446</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.44756944444444446</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0.23923611111111112</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0.23923611111111112</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0.23923611111111112</v>
+      </c>
+      <c r="K43" s="2">
+        <v>0.23923611111111112</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>43</v>
       </c>
@@ -1481,8 +2400,29 @@
       <c r="D44" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F44" t="s">
+        <v>77</v>
+      </c>
+      <c r="G44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s">
+        <v>77</v>
+      </c>
+      <c r="K44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
@@ -1492,8 +2432,29 @@
       <c r="D45" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G45" t="s">
+        <v>77</v>
+      </c>
+      <c r="H45" t="s">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s">
+        <v>77</v>
+      </c>
+      <c r="K45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>138</v>
       </c>
@@ -1503,25 +2464,87 @@
       <c r="D46" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E46" s="2">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="K46" s="2">
+        <v>0.23958333333333334</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C47" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" t="s">
+        <v>77</v>
+      </c>
+      <c r="H47" t="s">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s">
+        <v>77</v>
+      </c>
+      <c r="K47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>46</v>
       </c>
       <c r="C48" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s">
+        <v>77</v>
+      </c>
+      <c r="K48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>136</v>
       </c>
@@ -1531,669 +2554,2391 @@
       <c r="D49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E49" s="2">
+        <v>0.23993055555555554</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0.32326388888888885</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0.44826388888888885</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0.23993055555555554</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0.23993055555555554</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0.23993055555555554</v>
+      </c>
+      <c r="K49" s="2">
+        <v>0.23993055555555554</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C50" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" t="s">
+        <v>77</v>
+      </c>
+      <c r="H50" t="s">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s">
+        <v>77</v>
+      </c>
+      <c r="K50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C51" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
+        <v>77</v>
+      </c>
+      <c r="F51" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51" t="s">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>135</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E52" s="2">
+        <v>0.24027777777777778</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0.32361111111111113</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0.44861111111111113</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0.24027777777777778</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0.24027777777777778</v>
+      </c>
+      <c r="J52" s="2">
+        <v>0.24027777777777778</v>
+      </c>
+      <c r="K52" s="2">
+        <v>0.24027777777777778</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C53" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" t="s">
+        <v>77</v>
+      </c>
+      <c r="F53" t="s">
+        <v>77</v>
+      </c>
+      <c r="G53" t="s">
+        <v>77</v>
+      </c>
+      <c r="H53" t="s">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s">
+        <v>77</v>
+      </c>
+      <c r="K53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>52</v>
       </c>
       <c r="C54" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" t="s">
+        <v>77</v>
+      </c>
+      <c r="F54" t="s">
+        <v>77</v>
+      </c>
+      <c r="G54" t="s">
+        <v>77</v>
+      </c>
+      <c r="H54" t="s">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s">
+        <v>77</v>
+      </c>
+      <c r="K54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>53</v>
       </c>
       <c r="C55" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" t="s">
+        <v>77</v>
+      </c>
+      <c r="H55" t="s">
+        <v>77</v>
+      </c>
+      <c r="I55" t="s">
+        <v>77</v>
+      </c>
+      <c r="J55" t="s">
+        <v>77</v>
+      </c>
+      <c r="K55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>134</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E56" s="2">
+        <v>0.24097222222222223</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0.32430555555555557</v>
+      </c>
+      <c r="G56" s="2">
+        <v>0.44930555555555557</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0.24097222222222223</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0.24097222222222223</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.24097222222222223</v>
+      </c>
+      <c r="K56" s="2">
+        <v>0.24097222222222223</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>55</v>
       </c>
       <c r="C57" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" t="s">
+        <v>77</v>
+      </c>
+      <c r="F57" t="s">
+        <v>77</v>
+      </c>
+      <c r="G57" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s">
+        <v>77</v>
+      </c>
+      <c r="K57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>56</v>
       </c>
       <c r="C58" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" t="s">
+        <v>77</v>
+      </c>
+      <c r="F58" t="s">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H58" t="s">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C59" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>77</v>
+      </c>
+      <c r="E59" t="s">
+        <v>77</v>
+      </c>
+      <c r="F59" t="s">
+        <v>77</v>
+      </c>
+      <c r="G59" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" t="s">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s">
+        <v>77</v>
+      </c>
+      <c r="K59" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>133</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D60" t="s">
         <v>58</v>
       </c>
-      <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E60" s="2">
+        <v>0.24166666666666667</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0.24166666666666667</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0.24166666666666667</v>
+      </c>
+      <c r="J60" s="2">
+        <v>0.24166666666666667</v>
+      </c>
+      <c r="K60" s="2">
+        <v>0.24166666666666667</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>59</v>
       </c>
       <c r="C61" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>77</v>
+      </c>
+      <c r="E61" t="s">
+        <v>77</v>
+      </c>
+      <c r="F61" t="s">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s">
+        <v>77</v>
+      </c>
+      <c r="H61" t="s">
+        <v>77</v>
+      </c>
+      <c r="I61" t="s">
+        <v>77</v>
+      </c>
+      <c r="J61" t="s">
+        <v>77</v>
+      </c>
+      <c r="K61" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C62" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" t="s">
+        <v>77</v>
+      </c>
+      <c r="F62" t="s">
+        <v>77</v>
+      </c>
+      <c r="G62" t="s">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s">
+        <v>77</v>
+      </c>
+      <c r="K62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>61</v>
       </c>
       <c r="C63" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s">
+        <v>77</v>
+      </c>
+      <c r="K63" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>62</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D64" t="s">
         <v>63</v>
       </c>
-      <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E64" s="2">
+        <v>0.24201388888888889</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0.32534722222222223</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0.45034722222222223</v>
+      </c>
+      <c r="H64" s="2">
+        <v>0.24201388888888889</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0.24201388888888889</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0.24201388888888889</v>
+      </c>
+      <c r="K64" s="2">
+        <v>0.24201388888888889</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C65" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D65" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" t="s">
+        <v>77</v>
+      </c>
+      <c r="F65" t="s">
+        <v>77</v>
+      </c>
+      <c r="G65" t="s">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s">
+        <v>77</v>
+      </c>
+      <c r="K65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>78</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D66" t="s">
         <v>64</v>
       </c>
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E66" s="2">
+        <v>0.24224537037037039</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.32557870370370373</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0.45057870370370368</v>
+      </c>
+      <c r="H66" s="2">
+        <v>0.24224537037037039</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0.24224537037037039</v>
+      </c>
+      <c r="J66" s="2">
+        <v>0.24224537037037039</v>
+      </c>
+      <c r="K66" s="2">
+        <v>0.24224537037037039</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>80</v>
       </c>
       <c r="C67" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D67" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" t="s">
+        <v>77</v>
+      </c>
+      <c r="F67" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" t="s">
+        <v>77</v>
+      </c>
+      <c r="H67" t="s">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s">
+        <v>77</v>
+      </c>
+      <c r="K67" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>81</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D68" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>77</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D69" t="s">
         <v>65</v>
       </c>
-      <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E69" s="2">
+        <v>0.24236111111111111</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0.32569444444444445</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0.45069444444444445</v>
+      </c>
+      <c r="H69" s="2">
+        <v>0.24236111111111111</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0.24236111111111111</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0.24236111111111111</v>
+      </c>
+      <c r="K69" s="2">
+        <v>0.24236111111111111</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D70" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>83</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D71" t="s">
+        <v>77</v>
+      </c>
+      <c r="E71" t="s">
+        <v>77</v>
+      </c>
+      <c r="F71" t="s">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s">
+        <v>77</v>
+      </c>
+      <c r="H71" t="s">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s">
+        <v>77</v>
+      </c>
+      <c r="K71" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>84</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" t="s">
+        <v>77</v>
+      </c>
+      <c r="F72" t="s">
+        <v>77</v>
+      </c>
+      <c r="G72" t="s">
+        <v>77</v>
+      </c>
+      <c r="H72" t="s">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s">
+        <v>77</v>
+      </c>
+      <c r="K72" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>85</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D73" t="s">
+        <v>77</v>
+      </c>
+      <c r="E73" t="s">
+        <v>77</v>
+      </c>
+      <c r="F73" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" t="s">
+        <v>77</v>
+      </c>
+      <c r="H73" t="s">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s">
+        <v>77</v>
+      </c>
+      <c r="K73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D74" t="s">
         <v>66</v>
       </c>
-      <c r="G74" s="1"/>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E74" s="2">
+        <v>0.24270833333333333</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0.32604166666666667</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0.45104166666666662</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0.24270833333333333</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0.24270833333333333</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0.24270833333333333</v>
+      </c>
+      <c r="K74" s="2">
+        <v>0.24270833333333333</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>87</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D75" t="s">
+        <v>77</v>
+      </c>
+      <c r="E75" t="s">
+        <v>77</v>
+      </c>
+      <c r="F75" t="s">
+        <v>77</v>
+      </c>
+      <c r="G75" t="s">
+        <v>77</v>
+      </c>
+      <c r="H75" t="s">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D76" t="s">
+        <v>77</v>
+      </c>
+      <c r="E76" t="s">
+        <v>77</v>
+      </c>
+      <c r="F76" t="s">
+        <v>77</v>
+      </c>
+      <c r="G76" t="s">
+        <v>77</v>
+      </c>
+      <c r="H76" t="s">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s">
+        <v>77</v>
+      </c>
+      <c r="J76" t="s">
+        <v>77</v>
+      </c>
+      <c r="K76" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>89</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D77" t="s">
+        <v>77</v>
+      </c>
+      <c r="E77" t="s">
+        <v>77</v>
+      </c>
+      <c r="F77" t="s">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s">
+        <v>77</v>
+      </c>
+      <c r="K77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>90</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D78" t="s">
+        <v>77</v>
+      </c>
+      <c r="E78" t="s">
+        <v>77</v>
+      </c>
+      <c r="F78" t="s">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s">
+        <v>77</v>
+      </c>
+      <c r="H78" t="s">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D79" t="s">
         <v>67</v>
       </c>
-      <c r="G79" s="1"/>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E79" s="2">
+        <v>0.24340277777777777</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0.32673611111111112</v>
+      </c>
+      <c r="G79" s="2">
+        <v>0.45173611111111112</v>
+      </c>
+      <c r="H79" s="2">
+        <v>0.24340277777777777</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0.24340277777777777</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0.24340277777777777</v>
+      </c>
+      <c r="K79" s="2">
+        <v>0.24340277777777777</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80" t="s">
+        <v>77</v>
+      </c>
+      <c r="F80" t="s">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s">
+        <v>77</v>
+      </c>
+      <c r="H80" t="s">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D81" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" t="s">
+        <v>77</v>
+      </c>
+      <c r="F81" t="s">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s">
+        <v>77</v>
+      </c>
+      <c r="H81" t="s">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D82" t="s">
+        <v>77</v>
+      </c>
+      <c r="E82" t="s">
+        <v>77</v>
+      </c>
+      <c r="F82" t="s">
+        <v>77</v>
+      </c>
+      <c r="G82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s">
+        <v>77</v>
+      </c>
+      <c r="K82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D83" t="s">
         <v>68</v>
       </c>
-      <c r="G83" s="1"/>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E83" s="4">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0.32708333333333334</v>
+      </c>
+      <c r="G83" s="4">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="H83" s="4">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="I83" s="4">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="J83" s="4">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="K83" s="4">
+        <v>0.24374999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E84" t="s">
+        <v>77</v>
+      </c>
+      <c r="F84" t="s">
+        <v>77</v>
+      </c>
+      <c r="G84" t="s">
+        <v>77</v>
+      </c>
+      <c r="H84" t="s">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s">
+        <v>77</v>
+      </c>
+      <c r="K84" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D85" t="s">
+        <v>77</v>
+      </c>
+      <c r="E85" t="s">
+        <v>77</v>
+      </c>
+      <c r="F85" t="s">
+        <v>77</v>
+      </c>
+      <c r="G85" t="s">
+        <v>77</v>
+      </c>
+      <c r="H85" t="s">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D86" t="s">
+        <v>77</v>
+      </c>
+      <c r="E86" t="s">
+        <v>77</v>
+      </c>
+      <c r="F86" t="s">
+        <v>77</v>
+      </c>
+      <c r="G86" t="s">
+        <v>77</v>
+      </c>
+      <c r="H86" t="s">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D87" t="s">
         <v>69</v>
       </c>
-      <c r="G87" s="1"/>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E87" s="4">
+        <v>0.24432870370370371</v>
+      </c>
+      <c r="F87" s="4">
+        <v>0.32766203703703706</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0.45266203703703706</v>
+      </c>
+      <c r="H87" s="4">
+        <v>0.24432870370370371</v>
+      </c>
+      <c r="I87" s="4">
+        <v>0.24432870370370371</v>
+      </c>
+      <c r="J87" s="4">
+        <v>0.24432870370370371</v>
+      </c>
+      <c r="K87" s="4">
+        <v>0.24432870370370371</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>98</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D88" t="s">
+        <v>77</v>
+      </c>
+      <c r="E88" t="s">
+        <v>77</v>
+      </c>
+      <c r="F88" t="s">
+        <v>77</v>
+      </c>
+      <c r="G88" t="s">
+        <v>77</v>
+      </c>
+      <c r="H88" t="s">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>99</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D89" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89" t="s">
+        <v>77</v>
+      </c>
+      <c r="F89" t="s">
+        <v>77</v>
+      </c>
+      <c r="G89" t="s">
+        <v>77</v>
+      </c>
+      <c r="H89" t="s">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s">
+        <v>77</v>
+      </c>
+      <c r="K89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>100</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D90" t="s">
+        <v>77</v>
+      </c>
+      <c r="E90" t="s">
+        <v>77</v>
+      </c>
+      <c r="F90" t="s">
+        <v>77</v>
+      </c>
+      <c r="G90" t="s">
+        <v>77</v>
+      </c>
+      <c r="H90" t="s">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s">
+        <v>77</v>
+      </c>
+      <c r="K90" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>101</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D91" t="s">
+        <v>77</v>
+      </c>
+      <c r="E91" t="s">
+        <v>77</v>
+      </c>
+      <c r="F91" t="s">
+        <v>77</v>
+      </c>
+      <c r="G91" t="s">
+        <v>77</v>
+      </c>
+      <c r="H91" t="s">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>102</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D92" t="s">
+        <v>77</v>
+      </c>
+      <c r="E92" t="s">
+        <v>77</v>
+      </c>
+      <c r="F92" t="s">
+        <v>77</v>
+      </c>
+      <c r="G92" t="s">
+        <v>77</v>
+      </c>
+      <c r="H92" t="s">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s">
+        <v>77</v>
+      </c>
+      <c r="J92" t="s">
+        <v>77</v>
+      </c>
+      <c r="K92" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>103</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D93" t="s">
+        <v>77</v>
+      </c>
+      <c r="E93" t="s">
+        <v>77</v>
+      </c>
+      <c r="F93" t="s">
+        <v>77</v>
+      </c>
+      <c r="G93" t="s">
+        <v>77</v>
+      </c>
+      <c r="H93" t="s">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s">
+        <v>77</v>
+      </c>
+      <c r="K93" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>104</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D94" t="s">
+        <v>77</v>
+      </c>
+      <c r="E94" t="s">
+        <v>77</v>
+      </c>
+      <c r="F94" t="s">
+        <v>77</v>
+      </c>
+      <c r="G94" t="s">
+        <v>77</v>
+      </c>
+      <c r="H94" t="s">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s">
+        <v>77</v>
+      </c>
+      <c r="K94" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D95" t="s">
+        <v>77</v>
+      </c>
+      <c r="E95" t="s">
+        <v>77</v>
+      </c>
+      <c r="F95" t="s">
+        <v>77</v>
+      </c>
+      <c r="G95" t="s">
+        <v>77</v>
+      </c>
+      <c r="H95" t="s">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s">
+        <v>77</v>
+      </c>
+      <c r="K95" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D96" t="s">
+        <v>77</v>
+      </c>
+      <c r="E96" t="s">
+        <v>77</v>
+      </c>
+      <c r="F96" t="s">
+        <v>77</v>
+      </c>
+      <c r="G96" t="s">
+        <v>77</v>
+      </c>
+      <c r="H96" t="s">
+        <v>77</v>
+      </c>
+      <c r="I96" t="s">
+        <v>77</v>
+      </c>
+      <c r="J96" t="s">
+        <v>77</v>
+      </c>
+      <c r="K96" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D97" t="s">
+        <v>77</v>
+      </c>
+      <c r="E97" t="s">
+        <v>77</v>
+      </c>
+      <c r="F97" t="s">
+        <v>77</v>
+      </c>
+      <c r="G97" t="s">
+        <v>77</v>
+      </c>
+      <c r="H97" t="s">
+        <v>77</v>
+      </c>
+      <c r="I97" t="s">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s">
+        <v>77</v>
+      </c>
+      <c r="K97" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>108</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D98" t="s">
+        <v>77</v>
+      </c>
+      <c r="E98" t="s">
+        <v>77</v>
+      </c>
+      <c r="F98" t="s">
+        <v>77</v>
+      </c>
+      <c r="G98" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" t="s">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s">
+        <v>77</v>
+      </c>
+      <c r="K98" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>109</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D99" t="s">
+        <v>77</v>
+      </c>
+      <c r="E99" t="s">
+        <v>77</v>
+      </c>
+      <c r="F99" t="s">
+        <v>77</v>
+      </c>
+      <c r="G99" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" t="s">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s">
+        <v>77</v>
+      </c>
+      <c r="J99" t="s">
+        <v>77</v>
+      </c>
+      <c r="K99" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>110</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D100" t="s">
+        <v>77</v>
+      </c>
+      <c r="E100" t="s">
+        <v>77</v>
+      </c>
+      <c r="F100" t="s">
+        <v>77</v>
+      </c>
+      <c r="G100" t="s">
+        <v>77</v>
+      </c>
+      <c r="H100" t="s">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s">
+        <v>77</v>
+      </c>
+      <c r="J100" t="s">
+        <v>77</v>
+      </c>
+      <c r="K100" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>111</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D101" t="s">
+        <v>77</v>
+      </c>
+      <c r="E101" t="s">
+        <v>77</v>
+      </c>
+      <c r="F101" t="s">
+        <v>77</v>
+      </c>
+      <c r="G101" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" t="s">
+        <v>77</v>
+      </c>
+      <c r="I101" t="s">
+        <v>77</v>
+      </c>
+      <c r="J101" t="s">
+        <v>77</v>
+      </c>
+      <c r="K101" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>112</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D102" t="s">
+        <v>77</v>
+      </c>
+      <c r="E102" t="s">
+        <v>77</v>
+      </c>
+      <c r="F102" t="s">
+        <v>77</v>
+      </c>
+      <c r="G102" t="s">
+        <v>77</v>
+      </c>
+      <c r="H102" t="s">
+        <v>77</v>
+      </c>
+      <c r="I102" t="s">
+        <v>77</v>
+      </c>
+      <c r="J102" t="s">
+        <v>77</v>
+      </c>
+      <c r="K102" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>113</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D103" t="s">
+        <v>77</v>
+      </c>
+      <c r="E103" t="s">
+        <v>77</v>
+      </c>
+      <c r="F103" t="s">
+        <v>77</v>
+      </c>
+      <c r="G103" t="s">
+        <v>77</v>
+      </c>
+      <c r="H103" t="s">
+        <v>77</v>
+      </c>
+      <c r="I103" t="s">
+        <v>77</v>
+      </c>
+      <c r="J103" t="s">
+        <v>77</v>
+      </c>
+      <c r="K103" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>114</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D104" t="s">
         <v>70</v>
       </c>
-      <c r="G104" s="1"/>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E104" s="2">
+        <v>0.24583333333333335</v>
+      </c>
+      <c r="F104" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="G104" s="2">
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="H104" s="2">
+        <v>0.24583333333333335</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0.24583333333333335</v>
+      </c>
+      <c r="J104" s="2">
+        <v>0.24583333333333335</v>
+      </c>
+      <c r="K104" s="2">
+        <v>0.24583333333333335</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>115</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D105" t="s">
+        <v>77</v>
+      </c>
+      <c r="E105" t="s">
+        <v>77</v>
+      </c>
+      <c r="F105" t="s">
+        <v>77</v>
+      </c>
+      <c r="G105" t="s">
+        <v>77</v>
+      </c>
+      <c r="H105" t="s">
+        <v>77</v>
+      </c>
+      <c r="I105" t="s">
+        <v>77</v>
+      </c>
+      <c r="J105" t="s">
+        <v>77</v>
+      </c>
+      <c r="K105" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>116</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D106" t="s">
         <v>71</v>
       </c>
-      <c r="G106" s="1"/>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E106" s="2">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="F106" s="2">
+        <v>0.3298611111111111</v>
+      </c>
+      <c r="G106" s="2">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="H106" s="2">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="J106" s="2">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="K106" s="2">
+        <v>0.24652777777777779</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>117</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D107" t="s">
+        <v>77</v>
+      </c>
+      <c r="E107" t="s">
+        <v>77</v>
+      </c>
+      <c r="F107" t="s">
+        <v>77</v>
+      </c>
+      <c r="G107" t="s">
+        <v>77</v>
+      </c>
+      <c r="H107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107" t="s">
+        <v>77</v>
+      </c>
+      <c r="J107" t="s">
+        <v>77</v>
+      </c>
+      <c r="K107" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>77</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D108" t="s">
         <v>72</v>
       </c>
-      <c r="G108" s="1"/>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E108" s="4">
+        <v>0.24687499999999998</v>
+      </c>
+      <c r="F108" s="4">
+        <v>0.33020833333333333</v>
+      </c>
+      <c r="G108" s="4">
+        <v>0.45520833333333338</v>
+      </c>
+      <c r="H108" s="4">
+        <v>0.24687499999999998</v>
+      </c>
+      <c r="I108" s="4">
+        <v>0.24687499999999998</v>
+      </c>
+      <c r="J108" s="4">
+        <v>0.24687499999999998</v>
+      </c>
+      <c r="K108" s="4">
+        <v>0.24687499999999998</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>118</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D109" t="s">
+        <v>77</v>
+      </c>
+      <c r="E109" t="s">
+        <v>77</v>
+      </c>
+      <c r="F109" t="s">
+        <v>77</v>
+      </c>
+      <c r="G109" t="s">
+        <v>77</v>
+      </c>
+      <c r="H109" t="s">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s">
+        <v>77</v>
+      </c>
+      <c r="J109" t="s">
+        <v>77</v>
+      </c>
+      <c r="K109" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>119</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D110" t="s">
+        <v>77</v>
+      </c>
+      <c r="E110" t="s">
+        <v>77</v>
+      </c>
+      <c r="F110" t="s">
+        <v>77</v>
+      </c>
+      <c r="G110" t="s">
+        <v>77</v>
+      </c>
+      <c r="H110" t="s">
+        <v>77</v>
+      </c>
+      <c r="I110" t="s">
+        <v>77</v>
+      </c>
+      <c r="J110" t="s">
+        <v>77</v>
+      </c>
+      <c r="K110" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>120</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D111" t="s">
+        <v>77</v>
+      </c>
+      <c r="E111" t="s">
+        <v>77</v>
+      </c>
+      <c r="F111" t="s">
+        <v>77</v>
+      </c>
+      <c r="G111" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" t="s">
+        <v>77</v>
+      </c>
+      <c r="I111" t="s">
+        <v>77</v>
+      </c>
+      <c r="J111" t="s">
+        <v>77</v>
+      </c>
+      <c r="K111" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>121</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D112" t="s">
+        <v>77</v>
+      </c>
+      <c r="E112" t="s">
+        <v>77</v>
+      </c>
+      <c r="F112" t="s">
+        <v>77</v>
+      </c>
+      <c r="G112" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" t="s">
+        <v>77</v>
+      </c>
+      <c r="I112" t="s">
+        <v>77</v>
+      </c>
+      <c r="J112" t="s">
+        <v>77</v>
+      </c>
+      <c r="K112" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>122</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D113" t="s">
         <v>73</v>
       </c>
-      <c r="G113" s="1"/>
-    </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E113" s="2">
+        <v>0.24791666666666667</v>
+      </c>
+      <c r="F113" s="2">
+        <v>0.33124999999999999</v>
+      </c>
+      <c r="G113" s="2">
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="H113" s="2">
+        <v>0.24791666666666667</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0.24791666666666667</v>
+      </c>
+      <c r="J113" s="2">
+        <v>0.24791666666666667</v>
+      </c>
+      <c r="K113" s="2">
+        <v>0.24791666666666667</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>123</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D114" t="s">
+        <v>77</v>
+      </c>
+      <c r="E114" t="s">
+        <v>77</v>
+      </c>
+      <c r="F114" t="s">
+        <v>77</v>
+      </c>
+      <c r="G114" t="s">
+        <v>77</v>
+      </c>
+      <c r="H114" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114" t="s">
+        <v>77</v>
+      </c>
+      <c r="J114" t="s">
+        <v>77</v>
+      </c>
+      <c r="K114" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>124</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D115" t="s">
+        <v>77</v>
+      </c>
+      <c r="E115" t="s">
+        <v>77</v>
+      </c>
+      <c r="F115" t="s">
+        <v>77</v>
+      </c>
+      <c r="G115" t="s">
+        <v>77</v>
+      </c>
+      <c r="H115" t="s">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s">
+        <v>77</v>
+      </c>
+      <c r="J115" t="s">
+        <v>77</v>
+      </c>
+      <c r="K115" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>125</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D116" t="s">
+        <v>77</v>
+      </c>
+      <c r="E116" t="s">
+        <v>77</v>
+      </c>
+      <c r="F116" t="s">
+        <v>77</v>
+      </c>
+      <c r="G116" t="s">
+        <v>77</v>
+      </c>
+      <c r="H116" t="s">
+        <v>77</v>
+      </c>
+      <c r="I116" t="s">
+        <v>77</v>
+      </c>
+      <c r="J116" t="s">
+        <v>77</v>
+      </c>
+      <c r="K116" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>126</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D117" t="s">
         <v>74</v>
       </c>
-      <c r="G117" s="1"/>
-    </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E117" s="2">
+        <v>0.24861111111111112</v>
+      </c>
+      <c r="F117" s="2">
+        <v>0.33194444444444443</v>
+      </c>
+      <c r="G117" s="2">
+        <v>0.45694444444444443</v>
+      </c>
+      <c r="H117" s="2">
+        <v>0.24861111111111112</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0.24861111111111112</v>
+      </c>
+      <c r="J117" s="2">
+        <v>0.24861111111111112</v>
+      </c>
+      <c r="K117" s="2">
+        <v>0.24861111111111112</v>
+      </c>
+    </row>
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>127</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D118" t="s">
+        <v>77</v>
+      </c>
+      <c r="E118" t="s">
+        <v>77</v>
+      </c>
+      <c r="F118" t="s">
+        <v>77</v>
+      </c>
+      <c r="G118" t="s">
+        <v>77</v>
+      </c>
+      <c r="H118" t="s">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s">
+        <v>77</v>
+      </c>
+      <c r="J118" t="s">
+        <v>77</v>
+      </c>
+      <c r="K118" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>128</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D119" t="s">
         <v>75</v>
       </c>
-      <c r="G119" s="1"/>
-    </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E119" s="2">
+        <v>0.24930555555555556</v>
+      </c>
+      <c r="F119" s="2">
+        <v>0.33263888888888887</v>
+      </c>
+      <c r="G119" s="2">
+        <v>0.45763888888888887</v>
+      </c>
+      <c r="H119" s="2">
+        <v>0.24930555555555556</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0.24930555555555556</v>
+      </c>
+      <c r="J119" s="2">
+        <v>0.24930555555555556</v>
+      </c>
+      <c r="K119" s="2">
+        <v>0.24930555555555556</v>
+      </c>
+    </row>
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>129</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D120" t="s">
+        <v>77</v>
+      </c>
+      <c r="E120" t="s">
+        <v>77</v>
+      </c>
+      <c r="F120" t="s">
+        <v>77</v>
+      </c>
+      <c r="G120" t="s">
+        <v>77</v>
+      </c>
+      <c r="H120" t="s">
+        <v>77</v>
+      </c>
+      <c r="I120" t="s">
+        <v>77</v>
+      </c>
+      <c r="J120" t="s">
+        <v>77</v>
+      </c>
+      <c r="K120" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>130</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D121" t="s">
+        <v>77</v>
+      </c>
+      <c r="E121" t="s">
+        <v>77</v>
+      </c>
+      <c r="F121" t="s">
+        <v>77</v>
+      </c>
+      <c r="G121" t="s">
+        <v>77</v>
+      </c>
+      <c r="H121" t="s">
+        <v>77</v>
+      </c>
+      <c r="I121" t="s">
+        <v>77</v>
+      </c>
+      <c r="J121" t="s">
+        <v>77</v>
+      </c>
+      <c r="K121" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>131</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D122" t="s">
+        <v>77</v>
+      </c>
+      <c r="E122" t="s">
+        <v>77</v>
+      </c>
+      <c r="F122" t="s">
+        <v>77</v>
+      </c>
+      <c r="G122" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122" t="s">
+        <v>77</v>
+      </c>
+      <c r="I122" t="s">
+        <v>77</v>
+      </c>
+      <c r="J122" t="s">
+        <v>77</v>
+      </c>
+      <c r="K122" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>132</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D123" t="s">
         <v>76</v>
       </c>
-      <c r="G123" s="1"/>
-    </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E123" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F123" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G123" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H123" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="I123" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="J123" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="K123" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C124" s="1"/>
     </row>
   </sheetData>
